--- a/artfynd/A 10196-2026 artfynd.xlsx
+++ b/artfynd/A 10196-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050852</v>
       </c>
       <c r="B2" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132050859</v>
       </c>
       <c r="B3" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132050868</v>
       </c>
       <c r="B4" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132050876</v>
+        <v>132050867</v>
       </c>
       <c r="B5" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478636</v>
+        <v>478581</v>
       </c>
       <c r="R5" t="n">
-        <v>6991869</v>
+        <v>6991948</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Över 30 plantor</t>
+          <t>Minst 10 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132050867</v>
+        <v>132050876</v>
       </c>
       <c r="B6" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478581</v>
+        <v>478636</v>
       </c>
       <c r="R6" t="n">
-        <v>6991948</v>
+        <v>6991869</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 10 plantor</t>
+          <t>Över 30 plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,7 +1183,7 @@
         <v>132050888</v>
       </c>
       <c r="B7" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>132050890</v>
       </c>
       <c r="B8" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>132050869</v>
       </c>
       <c r="B9" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,57 +1476,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132050862</v>
+        <v>132050874</v>
       </c>
       <c r="B10" t="n">
-        <v>58065</v>
+        <v>99047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478616</v>
+        <v>478606</v>
       </c>
       <c r="R10" t="n">
-        <v>6991956</v>
+        <v>6991970</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,7 +1551,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 st, födosökande</t>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,45 +1578,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132050874</v>
+        <v>132050862</v>
       </c>
       <c r="B11" t="n">
-        <v>99046</v>
+        <v>58066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478606</v>
+        <v>478616</v>
       </c>
       <c r="R11" t="n">
-        <v>6991970</v>
+        <v>6991956</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>5 plantor</t>
+          <t>2 st, födosökande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132050880</v>
+        <v>132050850</v>
       </c>
       <c r="B12" t="n">
-        <v>57085</v>
+        <v>83249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1703,42 +1703,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478630</v>
+        <v>478651</v>
       </c>
       <c r="R12" t="n">
-        <v>6991950</v>
+        <v>6991858</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1771,11 +1763,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lockljud</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132050850</v>
+        <v>132050880</v>
       </c>
       <c r="B13" t="n">
-        <v>83248</v>
+        <v>57086</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,34 +1800,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478651</v>
+        <v>478630</v>
       </c>
       <c r="R13" t="n">
-        <v>6991858</v>
+        <v>6991950</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,6 +1868,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Lockljud</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132050875</v>
+        <v>132050889</v>
       </c>
       <c r="B14" t="n">
-        <v>99046</v>
+        <v>79269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478611</v>
+        <v>478616</v>
       </c>
       <c r="R14" t="n">
-        <v>6991957</v>
+        <v>6991993</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1970,11 +1970,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ca 5 plantor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,32 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132050889</v>
+        <v>132050875</v>
       </c>
       <c r="B15" t="n">
-        <v>79268</v>
+        <v>99047</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478616</v>
+        <v>478611</v>
       </c>
       <c r="R15" t="n">
-        <v>6991993</v>
+        <v>6991957</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,6 +2067,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ca 5 plantor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2101,7 +2101,7 @@
         <v>132050864</v>
       </c>
       <c r="B16" t="n">
-        <v>78280</v>
+        <v>78281</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>132050866</v>
       </c>
       <c r="B17" t="n">
-        <v>99046</v>
+        <v>99047</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 10196-2026 artfynd.xlsx
+++ b/artfynd/A 10196-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050852</v>
       </c>
       <c r="B2" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132050859</v>
       </c>
       <c r="B3" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132050868</v>
       </c>
       <c r="B4" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132050867</v>
+        <v>132050888</v>
       </c>
       <c r="B5" t="n">
-        <v>99047</v>
+        <v>79274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478581</v>
+        <v>478516</v>
       </c>
       <c r="R5" t="n">
-        <v>6991948</v>
+        <v>6991899</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132050876</v>
+        <v>132050867</v>
       </c>
       <c r="B6" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478636</v>
+        <v>478581</v>
       </c>
       <c r="R6" t="n">
-        <v>6991869</v>
+        <v>6991948</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,7 +1148,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Över 30 plantor</t>
+          <t>Minst 10 plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132050888</v>
+        <v>132050876</v>
       </c>
       <c r="B7" t="n">
-        <v>79269</v>
+        <v>99052</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478516</v>
+        <v>478636</v>
       </c>
       <c r="R7" t="n">
-        <v>6991899</v>
+        <v>6991869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Över 30 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,7 +1280,7 @@
         <v>132050890</v>
       </c>
       <c r="B8" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>132050869</v>
       </c>
       <c r="B9" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,45 +1476,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132050874</v>
+        <v>132050862</v>
       </c>
       <c r="B10" t="n">
-        <v>99047</v>
+        <v>58071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478606</v>
+        <v>478616</v>
       </c>
       <c r="R10" t="n">
-        <v>6991970</v>
+        <v>6991956</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1563,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>5 plantor</t>
+          <t>2 st, födosökande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,57 +1590,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132050862</v>
+        <v>132050874</v>
       </c>
       <c r="B11" t="n">
-        <v>58066</v>
+        <v>99052</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478616</v>
+        <v>478606</v>
       </c>
       <c r="R11" t="n">
-        <v>6991956</v>
+        <v>6991970</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 st, födosökande</t>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,7 +1695,7 @@
         <v>132050850</v>
       </c>
       <c r="B12" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>132050880</v>
       </c>
       <c r="B13" t="n">
-        <v>57086</v>
+        <v>57091</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>132050889</v>
       </c>
       <c r="B14" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>132050875</v>
       </c>
       <c r="B15" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>132050864</v>
       </c>
       <c r="B16" t="n">
-        <v>78281</v>
+        <v>78286</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>132050866</v>
       </c>
       <c r="B17" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 10196-2026 artfynd.xlsx
+++ b/artfynd/A 10196-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050852</v>
       </c>
       <c r="B2" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132050859</v>
       </c>
       <c r="B3" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>132050868</v>
       </c>
       <c r="B4" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>132050888</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>132050867</v>
       </c>
       <c r="B6" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>132050876</v>
       </c>
       <c r="B7" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>132050890</v>
       </c>
       <c r="B8" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>132050869</v>
       </c>
       <c r="B9" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,57 +1476,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132050862</v>
+        <v>132050874</v>
       </c>
       <c r="B10" t="n">
-        <v>58071</v>
+        <v>99054</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478616</v>
+        <v>478606</v>
       </c>
       <c r="R10" t="n">
-        <v>6991956</v>
+        <v>6991970</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,7 +1551,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 st, födosökande</t>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,45 +1578,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132050874</v>
+        <v>132050862</v>
       </c>
       <c r="B11" t="n">
-        <v>99052</v>
+        <v>58073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478606</v>
+        <v>478616</v>
       </c>
       <c r="R11" t="n">
-        <v>6991970</v>
+        <v>6991956</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>5 plantor</t>
+          <t>2 st, födosökande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,7 +1695,7 @@
         <v>132050850</v>
       </c>
       <c r="B12" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>132050880</v>
       </c>
       <c r="B13" t="n">
-        <v>57091</v>
+        <v>57093</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132050889</v>
+        <v>132050875</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>99054</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478616</v>
+        <v>478611</v>
       </c>
       <c r="R14" t="n">
-        <v>6991993</v>
+        <v>6991957</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1970,6 +1970,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ca 5 plantor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,32 +2001,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132050875</v>
+        <v>132050889</v>
       </c>
       <c r="B15" t="n">
-        <v>99052</v>
+        <v>79276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478611</v>
+        <v>478616</v>
       </c>
       <c r="R15" t="n">
-        <v>6991957</v>
+        <v>6991993</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,11 +2072,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ca 5 plantor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2101,7 +2101,7 @@
         <v>132050864</v>
       </c>
       <c r="B16" t="n">
-        <v>78286</v>
+        <v>78288</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>132050866</v>
       </c>
       <c r="B17" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 10196-2026 artfynd.xlsx
+++ b/artfynd/A 10196-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132050852</v>
       </c>
       <c r="B2" t="n">
-        <v>91872</v>
+        <v>91937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132050859</v>
+        <v>132050888</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478623</v>
+        <v>478516</v>
       </c>
       <c r="R3" t="n">
-        <v>6991872</v>
+        <v>6991899</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132050868</v>
+        <v>132050889</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478610</v>
+        <v>478616</v>
       </c>
       <c r="R4" t="n">
-        <v>6991959</v>
+        <v>6991993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132050888</v>
+        <v>132050890</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478516</v>
+        <v>478608</v>
       </c>
       <c r="R5" t="n">
-        <v>6991899</v>
+        <v>6991939</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132050876</v>
+        <v>132050850</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>83358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478636</v>
+        <v>478651</v>
       </c>
       <c r="R6" t="n">
-        <v>6991869</v>
+        <v>6991858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Över 30 plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132050867</v>
+        <v>132050859</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478581</v>
+        <v>478623</v>
       </c>
       <c r="R7" t="n">
-        <v>6991948</v>
+        <v>6991872</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1235,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 10 plantor</t>
+          <t>Ringhack, färska, på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,45 +1262,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132050890</v>
+        <v>132050880</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>57153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478608</v>
+        <v>478630</v>
       </c>
       <c r="R8" t="n">
-        <v>6991939</v>
+        <v>6991950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1341,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lockljud</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,45 +1372,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132050869</v>
+        <v>132050862</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478642</v>
+        <v>478616</v>
       </c>
       <c r="R9" t="n">
-        <v>6991826</v>
+        <v>6991956</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1459,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ca 20 plantor</t>
+          <t>2 st, födosökande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132050874</v>
+        <v>132050866</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478606</v>
+        <v>478607</v>
       </c>
       <c r="R10" t="n">
-        <v>6991970</v>
+        <v>6991916</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1561,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>5 plantor</t>
+          <t>Minst 30 plantor tätt ihop</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,57 +1588,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132050862</v>
+        <v>132050867</v>
       </c>
       <c r="B11" t="n">
-        <v>58114</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478616</v>
+        <v>478581</v>
       </c>
       <c r="R11" t="n">
-        <v>6991956</v>
+        <v>6991948</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1665,7 +1663,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 st, födosökande</t>
+          <t>Minst 10 plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,53 +1690,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132050880</v>
+        <v>132050868</v>
       </c>
       <c r="B12" t="n">
-        <v>57132</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svartsjöarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478630</v>
+        <v>478610</v>
       </c>
       <c r="R12" t="n">
-        <v>6991950</v>
+        <v>6991959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,7 +1765,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Lockljud</t>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,32 +1792,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132050850</v>
+        <v>132050869</v>
       </c>
       <c r="B13" t="n">
-        <v>83307</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1827,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478651</v>
+        <v>478642</v>
       </c>
       <c r="R13" t="n">
-        <v>6991858</v>
+        <v>6991826</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,6 +1863,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ca 20 plantor</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132050875</v>
+        <v>132050874</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1934,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478611</v>
+        <v>478606</v>
       </c>
       <c r="R14" t="n">
-        <v>6991957</v>
+        <v>6991970</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,7 +1969,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ca 5 plantor</t>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,32 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132050889</v>
+        <v>132050875</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478616</v>
+        <v>478611</v>
       </c>
       <c r="R15" t="n">
-        <v>6991993</v>
+        <v>6991957</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,6 +2067,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ca 5 plantor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2098,32 +2098,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132050864</v>
+        <v>132050876</v>
       </c>
       <c r="B16" t="n">
-        <v>78339</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478616</v>
+        <v>478636</v>
       </c>
       <c r="R16" t="n">
-        <v>6991993</v>
+        <v>6991869</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2169,6 +2169,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Över 30 plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2195,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132050866</v>
+        <v>132050877</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478607</v>
+        <v>478661</v>
       </c>
       <c r="R17" t="n">
-        <v>6991916</v>
+        <v>6991846</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,7 +2275,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 30 plantor tätt ihop</t>
+          <t>Ca 25 plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2294,6 +2299,103 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132050864</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svartsjöarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>478616</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6991993</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10196-2026 artfynd.xlsx
+++ b/artfynd/A 10196-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050852</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050888</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050889</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050890</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050850</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050859</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050880</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050862</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050866</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050867</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1789,6 +1844,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050868</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050869</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050874</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050875</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050876</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2299,6 +2379,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050877</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2396,8 +2481,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132050864</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>